--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.97869175123516</v>
+        <v>4.221537409575714</v>
       </c>
       <c r="D2" t="n">
-        <v>9.102591848603145</v>
+        <v>1.479171175398011</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F2" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.88895344409692</v>
+        <v>9.40695493466575</v>
       </c>
       <c r="D3" t="n">
-        <v>24.32719674677237</v>
+        <v>3.953169471350511</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F3" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.691087757150819</v>
+        <v>1.087301760537008</v>
       </c>
       <c r="D4" t="n">
-        <v>8.422396792655107</v>
+        <v>1.368639478806455</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F4" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.451160451437776</v>
+        <v>1.373313573358639</v>
       </c>
       <c r="D5" t="n">
-        <v>9.726563885842371</v>
+        <v>1.580566631449385</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F5" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.44571315660332</v>
+        <v>3.97242838794804</v>
       </c>
       <c r="D6" t="n">
-        <v>24.92810637196805</v>
+        <v>4.050817285444808</v>
       </c>
       <c r="E6" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F6" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.4435153329369</v>
+        <v>7.709571241602246</v>
       </c>
       <c r="D7" t="n">
-        <v>26.2306012268051</v>
+        <v>4.262472699355828</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F7" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.16708197338869</v>
+        <v>6.527150820675662</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03893833841815</v>
+        <v>4.068827479992949</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F8" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.26654833414195</v>
+        <v>7.680814104298068</v>
       </c>
       <c r="D9" t="n">
-        <v>35.60226301290544</v>
+        <v>5.785367739597134</v>
       </c>
       <c r="E9" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F9" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.9807432674851</v>
+        <v>5.846870780966328</v>
       </c>
       <c r="D10" t="n">
-        <v>23.18841211580539</v>
+        <v>3.768116968818376</v>
       </c>
       <c r="E10" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F10" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.30735843069361</v>
+        <v>6.874945744987712</v>
       </c>
       <c r="D11" t="n">
-        <v>10.93278383238925</v>
+        <v>1.776577372763253</v>
       </c>
       <c r="E11" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F11" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.69379676148724</v>
+        <v>6.612741973741677</v>
       </c>
       <c r="D12" t="n">
-        <v>49.81602760711532</v>
+        <v>8.09510448615624</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F12" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>6.41127710593266</v>
+        <v>1.041832529714057</v>
       </c>
       <c r="D13" t="n">
-        <v>2.840187480567994</v>
+        <v>0.461530465592299</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7067043045463</v>
+        <v>2.714839449488773</v>
       </c>
       <c r="F13" t="n">
-        <v>12.83299856729423</v>
+        <v>2.085362267185313</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
